--- a/defaults.xlsx
+++ b/defaults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Chaz.Larson/dev/github/test/PMM-quickstart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8950031-33C8-6A4E-81D4-C774643E95F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71184A7E-52C8-9D46-8BC6-C6391CDF5B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="760" windowWidth="21600" windowHeight="21580" xr2:uid="{7053105C-1802-6941-A9B7-4298D3DF8E7B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="21600" windowHeight="21580" xr2:uid="{7053105C-1802-6941-A9B7-4298D3DF8E7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="360">
   <si>
     <t>kind</t>
   </si>
@@ -1084,13 +1084,46 @@
   </si>
   <si>
     <t>mass_audience_rating_update</t>
+  </si>
+  <si>
+    <t>mass_critic_rating_update</t>
+  </si>
+  <si>
+    <t>mass_user_rating_update</t>
+  </si>
+  <si>
+    <t>mass_episode_audience_rating_update</t>
+  </si>
+  <si>
+    <t>mass_episode_critic_rating_update</t>
+  </si>
+  <si>
+    <t>mass_episode_user_rating_update</t>
+  </si>
+  <si>
+    <t>Radarr Add All</t>
+  </si>
+  <si>
+    <t>radarr_add_all</t>
+  </si>
+  <si>
+    <t>Adds every item in the library to Radarr. The existing paths in plex will be used as the root folder of each item, if the paths in Plex are not the same as your Radarr paths you can use the plex_path and radarr_path Radarr details to convert the paths.</t>
+  </si>
+  <si>
+    <t>Sonarr Add All</t>
+  </si>
+  <si>
+    <t>sonarr_add_all</t>
+  </si>
+  <si>
+    <t>Adds every item in the library to Sonarr. The existing paths in plex will be used as the root folder of each item, if the paths in Plex are not the same as your Sonarr paths you can use the plex_path and sonarr_path Sonarr details to convert the paths.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1103,6 +1136,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Var(--font-code)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1125,8 +1171,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1145,10 +1193,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF4EEB0A-8290-DA47-A85A-C435B8AE1372}" name="Table1" displayName="Table1" ref="A1:Q154" totalsRowShown="0">
-  <autoFilter ref="A1:Q154" xr:uid="{DF4EEB0A-8290-DA47-A85A-C435B8AE1372}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q154">
-    <sortCondition ref="B1:B154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF4EEB0A-8290-DA47-A85A-C435B8AE1372}" name="Table1" displayName="Table1" ref="A1:Q221" totalsRowShown="0">
+  <autoFilter ref="A1:Q221" xr:uid="{DF4EEB0A-8290-DA47-A85A-C435B8AE1372}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q221">
+    <sortCondition ref="A1:A221"/>
   </sortState>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{ECE09134-6BB4-0C41-84D2-F8FAA45E2029}" name="kind"/>
@@ -1189,7 +1237,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1477,7 +1525,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1485,8 +1533,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25693899-F9B1-7947-8587-CB479935A39A}">
-  <dimension ref="A1:Q154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S220"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
@@ -1508,7 +1556,7 @@
     <col min="18" max="26" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1609,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1580,11 +1628,14 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1607,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1630,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1653,7 +1704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1676,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1702,7 +1753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1728,7 +1779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1751,7 +1802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1774,7 +1825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1797,61 +1848,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1859,25 +1916,25 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -1885,11 +1942,11 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1897,13 +1954,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -1911,8 +1968,11 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1920,13 +1980,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1935,7 +1995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1943,13 +2003,13 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -1957,11 +2017,11 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1969,13 +2029,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -1983,11 +2043,8 @@
       <c r="H19" t="b">
         <v>1</v>
       </c>
-      <c r="O19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1995,13 +2052,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -2009,11 +2066,11 @@
       <c r="H20" t="b">
         <v>1</v>
       </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -2021,13 +2078,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -2035,109 +2092,91 @@
       <c r="H21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
-      <c r="H23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -2145,19 +2184,25 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -2165,19 +2210,19 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -2185,19 +2230,22 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -2205,19 +2253,25 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2225,25 +2279,22 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -2251,19 +2302,22 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -2271,13 +2325,13 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -2286,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -2294,13 +2348,13 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -2308,11 +2362,8 @@
       <c r="H33" t="b">
         <v>1</v>
       </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -2320,13 +2371,13 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -2335,7 +2386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -2343,13 +2394,13 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -2358,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -2366,13 +2417,13 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -2381,7 +2432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -2389,13 +2440,13 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -2404,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -2412,13 +2463,13 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -2426,8 +2477,11 @@
       <c r="H38" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -2435,13 +2489,13 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -2450,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -2458,13 +2512,13 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -2473,7 +2527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -2481,13 +2535,13 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -2496,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -2504,13 +2558,13 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -2518,11 +2572,8 @@
       <c r="H42" t="b">
         <v>1</v>
       </c>
-      <c r="M42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -2530,13 +2581,13 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -2545,7 +2596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -2553,13 +2604,13 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -2568,113 +2619,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>354</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
-      <c r="H45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>357</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>358</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" t="b">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -2682,31 +2733,37 @@
       <c r="H49" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
       </c>
-      <c r="H50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -2714,13 +2771,13 @@
         <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E51" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -2729,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>1</v>
       </c>
@@ -2737,13 +2794,13 @@
         <v>194</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E52" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -2752,7 +2809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>1</v>
       </c>
@@ -2760,13 +2817,13 @@
         <v>194</v>
       </c>
       <c r="C53" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D53" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -2775,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>1</v>
       </c>
@@ -2783,13 +2840,13 @@
         <v>194</v>
       </c>
       <c r="C54" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D54" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E54" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -2798,7 +2855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -2806,13 +2863,13 @@
         <v>194</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D55" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -2821,7 +2878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>1</v>
       </c>
@@ -2829,13 +2886,13 @@
         <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D56" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -2844,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>1</v>
       </c>
@@ -2852,13 +2909,13 @@
         <v>194</v>
       </c>
       <c r="C57" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E57" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -2867,7 +2924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>1</v>
       </c>
@@ -2875,50 +2932,68 @@
         <v>194</v>
       </c>
       <c r="C58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E58" t="s">
+        <v>218</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" t="s">
+        <v>220</v>
+      </c>
+      <c r="E59" t="s">
+        <v>221</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C60" t="s">
         <v>222</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D60" t="s">
         <v>223</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E60" t="s">
         <v>224</v>
       </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>2</v>
-      </c>
-      <c r="B59" t="s">
-        <v>217</v>
-      </c>
-      <c r="D59" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>2</v>
-      </c>
-      <c r="B60" t="s">
-        <v>217</v>
-      </c>
-      <c r="D60" t="s">
-        <v>227</v>
-      </c>
-      <c r="E60" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2926,13 +3001,13 @@
         <v>217</v>
       </c>
       <c r="D61" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="E61" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2940,41 +3015,41 @@
         <v>217</v>
       </c>
       <c r="D62" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" t="s">
         <v>230</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E64" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>223</v>
-      </c>
-      <c r="D63" t="s">
-        <v>232</v>
-      </c>
-      <c r="E63" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>2</v>
-      </c>
-      <c r="B64" t="s">
-        <v>223</v>
-      </c>
-      <c r="D64" t="s">
-        <v>234</v>
-      </c>
-      <c r="E64" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2982,13 +3057,13 @@
         <v>223</v>
       </c>
       <c r="D65" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E65" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2996,41 +3071,41 @@
         <v>223</v>
       </c>
       <c r="D66" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>223</v>
+      </c>
+      <c r="D67" t="s">
+        <v>236</v>
+      </c>
+      <c r="E67" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>223</v>
+      </c>
+      <c r="D68" t="s">
         <v>238</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E68" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" t="s">
-        <v>199</v>
-      </c>
-      <c r="D67" t="s">
-        <v>225</v>
-      </c>
-      <c r="E67" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>2</v>
-      </c>
-      <c r="B68" t="s">
-        <v>199</v>
-      </c>
-      <c r="D68" t="s">
-        <v>250</v>
-      </c>
-      <c r="E68" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>2</v>
       </c>
@@ -3038,13 +3113,13 @@
         <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -3052,13 +3127,13 @@
         <v>199</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -3066,19 +3141,13 @@
         <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E71" t="s">
-        <v>242</v>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -3086,19 +3155,13 @@
         <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E72" t="s">
-        <v>244</v>
-      </c>
-      <c r="J72" t="b">
-        <v>1</v>
-      </c>
-      <c r="N72" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -3106,19 +3169,19 @@
         <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E73" t="s">
-        <v>246</v>
-      </c>
-      <c r="J73" t="b">
-        <v>1</v>
-      </c>
-      <c r="N73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -3126,10 +3189,10 @@
         <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
@@ -3138,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -3146,53 +3209,59 @@
         <v>199</v>
       </c>
       <c r="D75" t="s">
+        <v>245</v>
+      </c>
+      <c r="E75" t="s">
+        <v>246</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>199</v>
+      </c>
+      <c r="D76" t="s">
+        <v>247</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>199</v>
+      </c>
+      <c r="D77" t="s">
         <v>16</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E77" t="s">
         <v>249</v>
       </c>
-      <c r="K75" t="b">
-        <v>1</v>
-      </c>
-      <c r="P75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" t="s">
-        <v>255</v>
-      </c>
-      <c r="D76" t="s">
-        <v>80</v>
-      </c>
-      <c r="E76" t="s">
-        <v>256</v>
-      </c>
-      <c r="J76" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>2</v>
-      </c>
-      <c r="B77" t="s">
-        <v>255</v>
-      </c>
-      <c r="D77" t="s">
-        <v>225</v>
-      </c>
-      <c r="E77" t="s">
-        <v>257</v>
-      </c>
-      <c r="J77" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="P77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -3200,16 +3269,16 @@
         <v>255</v>
       </c>
       <c r="D78" t="s">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>2</v>
       </c>
@@ -3217,16 +3286,16 @@
         <v>255</v>
       </c>
       <c r="D79" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E79" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -3234,16 +3303,16 @@
         <v>255</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -3251,47 +3320,50 @@
         <v>255</v>
       </c>
       <c r="D81" t="s">
+        <v>252</v>
+      </c>
+      <c r="E81" t="s">
+        <v>259</v>
+      </c>
+      <c r="J81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>255</v>
+      </c>
+      <c r="D82" t="s">
+        <v>131</v>
+      </c>
+      <c r="E82" t="s">
+        <v>260</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>255</v>
+      </c>
+      <c r="D83" t="s">
         <v>230</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E83" t="s">
         <v>261</v>
       </c>
-      <c r="J81" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B82" t="s">
-        <v>196</v>
-      </c>
-      <c r="D82" t="s">
-        <v>262</v>
-      </c>
-      <c r="E82" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B83" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" t="s">
         <v>2</v>
       </c>
@@ -3299,13 +3371,16 @@
         <v>196</v>
       </c>
       <c r="D84" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E84" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85" t="s">
         <v>2</v>
       </c>
@@ -3313,13 +3388,13 @@
         <v>196</v>
       </c>
       <c r="D85" t="s">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="E85" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86" t="s">
         <v>2</v>
       </c>
@@ -3327,13 +3402,13 @@
         <v>196</v>
       </c>
       <c r="D86" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E86" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" t="s">
         <v>2</v>
       </c>
@@ -3341,13 +3416,13 @@
         <v>196</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="E87" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88" t="s">
         <v>2</v>
       </c>
@@ -3355,13 +3430,13 @@
         <v>196</v>
       </c>
       <c r="D88" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
       <c r="A89" t="s">
         <v>2</v>
       </c>
@@ -3369,13 +3444,13 @@
         <v>196</v>
       </c>
       <c r="D89" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="E89" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90" t="s">
         <v>2</v>
       </c>
@@ -3383,19 +3458,13 @@
         <v>196</v>
       </c>
       <c r="D90" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>266</v>
-      </c>
-      <c r="I90" t="b">
-        <v>1</v>
-      </c>
-      <c r="M90" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91" t="s">
         <v>2</v>
       </c>
@@ -3403,53 +3472,53 @@
         <v>196</v>
       </c>
       <c r="D91" t="s">
+        <v>230</v>
+      </c>
+      <c r="E91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" t="s">
+        <v>241</v>
+      </c>
+      <c r="E92" t="s">
+        <v>266</v>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="M92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17">
+      <c r="A93" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" t="s">
         <v>16</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E93" t="s">
         <v>267</v>
       </c>
-      <c r="K91" t="b">
-        <v>1</v>
-      </c>
-      <c r="P91" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>2</v>
-      </c>
-      <c r="B92" t="s">
-        <v>202</v>
-      </c>
-      <c r="D92" t="s">
-        <v>262</v>
-      </c>
-      <c r="E92" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q92" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>2</v>
-      </c>
-      <c r="B93" t="s">
-        <v>202</v>
-      </c>
-      <c r="D93" t="s">
-        <v>275</v>
-      </c>
-      <c r="E93" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
+      <c r="P93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
       <c r="A94" t="s">
         <v>2</v>
       </c>
@@ -3457,13 +3526,16 @@
         <v>202</v>
       </c>
       <c r="D94" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E94" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
       <c r="A95" t="s">
         <v>2</v>
       </c>
@@ -3471,13 +3543,16 @@
         <v>202</v>
       </c>
       <c r="D95" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="E95" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96" t="s">
         <v>2</v>
       </c>
@@ -3485,13 +3560,13 @@
         <v>202</v>
       </c>
       <c r="D96" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E96" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -3499,13 +3574,13 @@
         <v>202</v>
       </c>
       <c r="D97" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E97" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17">
       <c r="A98" t="s">
         <v>2</v>
       </c>
@@ -3513,19 +3588,13 @@
         <v>202</v>
       </c>
       <c r="D98" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E98" t="s">
-        <v>278</v>
-      </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="M98" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17">
       <c r="A99" t="s">
         <v>2</v>
       </c>
@@ -3533,19 +3602,13 @@
         <v>202</v>
       </c>
       <c r="D99" t="s">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="E99" t="s">
-        <v>280</v>
-      </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="M99" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17">
       <c r="A100" t="s">
         <v>2</v>
       </c>
@@ -3553,50 +3616,59 @@
         <v>202</v>
       </c>
       <c r="D100" t="s">
+        <v>241</v>
+      </c>
+      <c r="E100" t="s">
+        <v>278</v>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="M100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" t="s">
+        <v>202</v>
+      </c>
+      <c r="D101" t="s">
+        <v>279</v>
+      </c>
+      <c r="E101" t="s">
+        <v>280</v>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+      <c r="M101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" t="s">
         <v>281</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E102" t="s">
         <v>282</v>
       </c>
-      <c r="I100" t="b">
-        <v>1</v>
-      </c>
-      <c r="M100" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>2</v>
-      </c>
-      <c r="B101" t="s">
-        <v>205</v>
-      </c>
-      <c r="D101" t="s">
-        <v>262</v>
-      </c>
-      <c r="E101" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q101" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>2</v>
-      </c>
-      <c r="B102" t="s">
-        <v>205</v>
-      </c>
-      <c r="D102" t="s">
-        <v>225</v>
-      </c>
-      <c r="E102" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="M102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17">
       <c r="A103" t="s">
         <v>2</v>
       </c>
@@ -3604,13 +3676,16 @@
         <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E103" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17">
       <c r="A104" t="s">
         <v>2</v>
       </c>
@@ -3618,13 +3693,13 @@
         <v>205</v>
       </c>
       <c r="D104" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E104" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17">
       <c r="A105" t="s">
         <v>2</v>
       </c>
@@ -3632,13 +3707,13 @@
         <v>205</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="E105" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17">
       <c r="A106" t="s">
         <v>2</v>
       </c>
@@ -3646,13 +3721,13 @@
         <v>205</v>
       </c>
       <c r="D106" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E106" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17">
       <c r="A107" t="s">
         <v>2</v>
       </c>
@@ -3660,13 +3735,13 @@
         <v>205</v>
       </c>
       <c r="D107" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="E107" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17">
       <c r="A108" t="s">
         <v>2</v>
       </c>
@@ -3674,19 +3749,13 @@
         <v>205</v>
       </c>
       <c r="D108" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E108" t="s">
-        <v>288</v>
-      </c>
-      <c r="I108" t="b">
-        <v>1</v>
-      </c>
-      <c r="M108" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17">
       <c r="A109" t="s">
         <v>2</v>
       </c>
@@ -3694,19 +3763,13 @@
         <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E109" t="s">
-        <v>289</v>
-      </c>
-      <c r="J109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N109" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3714,44 +3777,56 @@
         <v>205</v>
       </c>
       <c r="D110" t="s">
+        <v>241</v>
+      </c>
+      <c r="E110" t="s">
+        <v>288</v>
+      </c>
+      <c r="I110" t="b">
+        <v>1</v>
+      </c>
+      <c r="M110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17">
+      <c r="A111" t="s">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>205</v>
+      </c>
+      <c r="D111" t="s">
+        <v>243</v>
+      </c>
+      <c r="E111" t="s">
+        <v>289</v>
+      </c>
+      <c r="J111" t="b">
+        <v>1</v>
+      </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>205</v>
+      </c>
+      <c r="D112" t="s">
         <v>16</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E112" t="s">
         <v>290</v>
       </c>
-      <c r="K110" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>2</v>
-      </c>
-      <c r="B111" t="s">
-        <v>214</v>
-      </c>
-      <c r="D111" t="s">
-        <v>225</v>
-      </c>
-      <c r="E111" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>2</v>
-      </c>
-      <c r="B112" t="s">
-        <v>214</v>
-      </c>
-      <c r="D112" t="s">
-        <v>227</v>
-      </c>
-      <c r="E112" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17">
       <c r="A113" t="s">
         <v>2</v>
       </c>
@@ -3759,13 +3834,13 @@
         <v>214</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="E113" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17">
       <c r="A114" t="s">
         <v>2</v>
       </c>
@@ -3773,47 +3848,41 @@
         <v>214</v>
       </c>
       <c r="D114" t="s">
+        <v>227</v>
+      </c>
+      <c r="E114" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17">
+      <c r="A115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>214</v>
+      </c>
+      <c r="D115" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17">
+      <c r="A116" t="s">
+        <v>2</v>
+      </c>
+      <c r="B116" t="s">
+        <v>214</v>
+      </c>
+      <c r="D116" t="s">
         <v>230</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E116" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>2</v>
-      </c>
-      <c r="B115" t="s">
-        <v>348</v>
-      </c>
-      <c r="D115" t="s">
-        <v>300</v>
-      </c>
-      <c r="E115" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q115" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>2</v>
-      </c>
-      <c r="B116" t="s">
-        <v>348</v>
-      </c>
-      <c r="D116" t="s">
-        <v>302</v>
-      </c>
-      <c r="E116" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q116" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17">
       <c r="A117" t="s">
         <v>2</v>
       </c>
@@ -3821,16 +3890,22 @@
         <v>348</v>
       </c>
       <c r="D117" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E117" t="s">
-        <v>305</v>
+        <v>301</v>
+      </c>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" t="b">
+        <v>1</v>
       </c>
       <c r="Q117" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:17">
       <c r="A118" t="s">
         <v>2</v>
       </c>
@@ -3838,13 +3913,22 @@
         <v>348</v>
       </c>
       <c r="D118" t="s">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E118" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17">
       <c r="A119" t="s">
         <v>2</v>
       </c>
@@ -3852,13 +3936,22 @@
         <v>348</v>
       </c>
       <c r="D119" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="E119" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17">
       <c r="A120" t="s">
         <v>2</v>
       </c>
@@ -3866,13 +3959,19 @@
         <v>348</v>
       </c>
       <c r="D120" t="s">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E120" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3880,13 +3979,19 @@
         <v>348</v>
       </c>
       <c r="D121" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E121" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3894,13 +3999,19 @@
         <v>348</v>
       </c>
       <c r="D122" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="E122" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17">
       <c r="A123" t="s">
         <v>2</v>
       </c>
@@ -3908,19 +4019,19 @@
         <v>348</v>
       </c>
       <c r="D123" t="s">
-        <v>329</v>
+        <v>252</v>
       </c>
       <c r="E123" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
       </c>
-      <c r="K123" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17">
       <c r="A124" t="s">
         <v>2</v>
       </c>
@@ -3928,13 +4039,19 @@
         <v>348</v>
       </c>
       <c r="D124" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="E124" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17">
       <c r="A125" t="s">
         <v>2</v>
       </c>
@@ -3942,19 +4059,22 @@
         <v>348</v>
       </c>
       <c r="D125" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="E125" t="s">
-        <v>306</v>
-      </c>
-      <c r="I125" t="b">
-        <v>1</v>
-      </c>
-      <c r="M125" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17">
       <c r="A126" t="s">
         <v>2</v>
       </c>
@@ -3962,19 +4082,19 @@
         <v>348</v>
       </c>
       <c r="D126" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
-      </c>
-      <c r="J126" t="b">
-        <v>1</v>
-      </c>
-      <c r="N126" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17">
       <c r="A127" t="s">
         <v>2</v>
       </c>
@@ -3982,19 +4102,22 @@
         <v>348</v>
       </c>
       <c r="D127" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
-      </c>
-      <c r="J127" t="b">
-        <v>1</v>
-      </c>
-      <c r="N127" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+      <c r="F127" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+      <c r="M127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -4002,19 +4125,22 @@
         <v>348</v>
       </c>
       <c r="D128" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="E128" t="s">
-        <v>311</v>
-      </c>
-      <c r="J128" t="b">
+        <v>307</v>
+      </c>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+      <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:17">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -4022,19 +4148,22 @@
         <v>348</v>
       </c>
       <c r="D129" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>313</v>
-      </c>
-      <c r="J129" t="b">
+        <v>309</v>
+      </c>
+      <c r="F129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G129" t="b">
         <v>1</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:17">
       <c r="A130" t="s">
         <v>2</v>
       </c>
@@ -4042,19 +4171,22 @@
         <v>348</v>
       </c>
       <c r="D130" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E130" t="s">
-        <v>315</v>
-      </c>
-      <c r="J130" t="b">
+        <v>311</v>
+      </c>
+      <c r="F130" t="b">
+        <v>1</v>
+      </c>
+      <c r="G130" t="b">
         <v>1</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:17">
       <c r="A131" t="s">
         <v>2</v>
       </c>
@@ -4062,19 +4194,22 @@
         <v>348</v>
       </c>
       <c r="D131" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E131" t="s">
-        <v>317</v>
-      </c>
-      <c r="J131" t="b">
+        <v>313</v>
+      </c>
+      <c r="F131" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" t="b">
         <v>1</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:17">
       <c r="A132" t="s">
         <v>2</v>
       </c>
@@ -4082,19 +4217,22 @@
         <v>348</v>
       </c>
       <c r="D132" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E132" t="s">
-        <v>319</v>
-      </c>
-      <c r="J132" t="b">
+        <v>315</v>
+      </c>
+      <c r="F132" t="b">
+        <v>1</v>
+      </c>
+      <c r="G132" t="b">
         <v>1</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:17">
       <c r="A133" t="s">
         <v>2</v>
       </c>
@@ -4102,19 +4240,22 @@
         <v>348</v>
       </c>
       <c r="D133" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E133" t="s">
-        <v>321</v>
-      </c>
-      <c r="J133" t="b">
+        <v>317</v>
+      </c>
+      <c r="F133" t="b">
+        <v>1</v>
+      </c>
+      <c r="G133" t="b">
         <v>1</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:17">
       <c r="A134" t="s">
         <v>2</v>
       </c>
@@ -4122,19 +4263,22 @@
         <v>348</v>
       </c>
       <c r="D134" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E134" t="s">
-        <v>323</v>
-      </c>
-      <c r="J134" t="b">
+        <v>319</v>
+      </c>
+      <c r="F134" t="b">
+        <v>1</v>
+      </c>
+      <c r="G134" t="b">
         <v>1</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:17">
       <c r="A135" t="s">
         <v>2</v>
       </c>
@@ -4142,19 +4286,22 @@
         <v>348</v>
       </c>
       <c r="D135" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E135" t="s">
-        <v>325</v>
-      </c>
-      <c r="J135" t="b">
+        <v>321</v>
+      </c>
+      <c r="F135" t="b">
+        <v>1</v>
+      </c>
+      <c r="G135" t="b">
         <v>1</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:17">
       <c r="A136" t="s">
         <v>2</v>
       </c>
@@ -4162,19 +4309,22 @@
         <v>348</v>
       </c>
       <c r="D136" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E136" t="s">
-        <v>327</v>
-      </c>
-      <c r="J136" t="b">
+        <v>323</v>
+      </c>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
+      <c r="G136" t="b">
         <v>1</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:17">
       <c r="A137" t="s">
         <v>2</v>
       </c>
@@ -4182,460 +4332,1908 @@
         <v>348</v>
       </c>
       <c r="D137" t="s">
+        <v>324</v>
+      </c>
+      <c r="E137" t="s">
+        <v>325</v>
+      </c>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" t="b">
+        <v>1</v>
+      </c>
+      <c r="N137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17">
+      <c r="A138" t="s">
+        <v>2</v>
+      </c>
+      <c r="B138" t="s">
+        <v>348</v>
+      </c>
+      <c r="D138" t="s">
+        <v>326</v>
+      </c>
+      <c r="E138" t="s">
+        <v>327</v>
+      </c>
+      <c r="F138" t="b">
+        <v>1</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+      <c r="N138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17">
+      <c r="A139" t="s">
+        <v>2</v>
+      </c>
+      <c r="B139" t="s">
+        <v>348</v>
+      </c>
+      <c r="D139" t="s">
         <v>16</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E139" t="s">
         <v>328</v>
       </c>
-      <c r="K137" t="b">
-        <v>1</v>
-      </c>
-      <c r="P137" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+      <c r="F139" t="b">
+        <v>1</v>
+      </c>
+      <c r="G139" t="b">
+        <v>1</v>
+      </c>
+      <c r="P139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" t="s">
+        <v>2</v>
+      </c>
+      <c r="B140" t="s">
+        <v>349</v>
+      </c>
+      <c r="D140" t="s">
+        <v>300</v>
+      </c>
+      <c r="E140" t="s">
+        <v>301</v>
+      </c>
+      <c r="F140" t="b">
+        <v>1</v>
+      </c>
+      <c r="H140" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+      <c r="B141" t="s">
+        <v>349</v>
+      </c>
+      <c r="D141" t="s">
+        <v>302</v>
+      </c>
+      <c r="E141" t="s">
+        <v>303</v>
+      </c>
+      <c r="F141" t="b">
+        <v>1</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17">
+      <c r="A142" t="s">
+        <v>2</v>
+      </c>
+      <c r="B142" t="s">
+        <v>349</v>
+      </c>
+      <c r="D142" t="s">
+        <v>304</v>
+      </c>
+      <c r="E142" t="s">
+        <v>305</v>
+      </c>
+      <c r="F142" t="b">
+        <v>1</v>
+      </c>
+      <c r="H142" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17">
+      <c r="A143" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>349</v>
+      </c>
+      <c r="D143" t="s">
+        <v>80</v>
+      </c>
+      <c r="E143" t="s">
+        <v>256</v>
+      </c>
+      <c r="F143" t="b">
+        <v>1</v>
+      </c>
+      <c r="H143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17">
+      <c r="A144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>349</v>
+      </c>
+      <c r="D144" t="s">
+        <v>225</v>
+      </c>
+      <c r="E144" t="s">
+        <v>257</v>
+      </c>
+      <c r="F144" t="b">
+        <v>1</v>
+      </c>
+      <c r="H144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
+      <c r="A145" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" t="s">
+        <v>349</v>
+      </c>
+      <c r="D145" t="s">
+        <v>250</v>
+      </c>
+      <c r="E145" t="s">
+        <v>258</v>
+      </c>
+      <c r="F145" t="b">
+        <v>1</v>
+      </c>
+      <c r="H145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14">
+      <c r="A146" t="s">
+        <v>2</v>
+      </c>
+      <c r="B146" t="s">
+        <v>349</v>
+      </c>
+      <c r="D146" t="s">
+        <v>252</v>
+      </c>
+      <c r="E146" t="s">
+        <v>259</v>
+      </c>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+      <c r="H146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14">
+      <c r="A147" t="s">
+        <v>2</v>
+      </c>
+      <c r="B147" t="s">
+        <v>349</v>
+      </c>
+      <c r="D147" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" t="s">
+        <v>260</v>
+      </c>
+      <c r="F147" t="b">
+        <v>1</v>
+      </c>
+      <c r="H147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14">
+      <c r="A148" t="s">
+        <v>2</v>
+      </c>
+      <c r="B148" t="s">
+        <v>349</v>
+      </c>
+      <c r="D148" t="s">
+        <v>329</v>
+      </c>
+      <c r="E148" t="s">
+        <v>330</v>
+      </c>
+      <c r="F148" t="b">
+        <v>1</v>
+      </c>
+      <c r="H148" t="b">
+        <v>1</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>349</v>
+      </c>
+      <c r="D149" t="s">
+        <v>230</v>
+      </c>
+      <c r="E149" t="s">
+        <v>261</v>
+      </c>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+      <c r="H149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>349</v>
+      </c>
+      <c r="D150" t="s">
+        <v>241</v>
+      </c>
+      <c r="E150" t="s">
+        <v>306</v>
+      </c>
+      <c r="F150" t="b">
+        <v>1</v>
+      </c>
+      <c r="H150" t="b">
+        <v>1</v>
+      </c>
+      <c r="M150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14">
+      <c r="A151" t="s">
+        <v>2</v>
+      </c>
+      <c r="B151" t="s">
+        <v>349</v>
+      </c>
+      <c r="D151" t="s">
+        <v>243</v>
+      </c>
+      <c r="E151" t="s">
+        <v>307</v>
+      </c>
+      <c r="F151" t="b">
+        <v>1</v>
+      </c>
+      <c r="H151" t="b">
+        <v>1</v>
+      </c>
+      <c r="N151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
+      <c r="A152" t="s">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>349</v>
+      </c>
+      <c r="D152" t="s">
+        <v>308</v>
+      </c>
+      <c r="E152" t="s">
+        <v>309</v>
+      </c>
+      <c r="F152" t="b">
+        <v>1</v>
+      </c>
+      <c r="H152" t="b">
+        <v>1</v>
+      </c>
+      <c r="N152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>349</v>
+      </c>
+      <c r="D153" t="s">
+        <v>310</v>
+      </c>
+      <c r="E153" t="s">
+        <v>311</v>
+      </c>
+      <c r="F153" t="b">
+        <v>1</v>
+      </c>
+      <c r="H153" t="b">
+        <v>1</v>
+      </c>
+      <c r="N153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
+      <c r="A154" t="s">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>349</v>
+      </c>
+      <c r="D154" t="s">
+        <v>312</v>
+      </c>
+      <c r="E154" t="s">
+        <v>313</v>
+      </c>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+      <c r="H154" t="b">
+        <v>1</v>
+      </c>
+      <c r="N154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14">
+      <c r="A155" t="s">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>349</v>
+      </c>
+      <c r="D155" t="s">
+        <v>314</v>
+      </c>
+      <c r="E155" t="s">
+        <v>315</v>
+      </c>
+      <c r="F155" t="b">
+        <v>1</v>
+      </c>
+      <c r="H155" t="b">
+        <v>1</v>
+      </c>
+      <c r="N155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>349</v>
+      </c>
+      <c r="D156" t="s">
+        <v>316</v>
+      </c>
+      <c r="E156" t="s">
+        <v>317</v>
+      </c>
+      <c r="F156" t="b">
+        <v>1</v>
+      </c>
+      <c r="H156" t="b">
+        <v>1</v>
+      </c>
+      <c r="N156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14">
+      <c r="A157" t="s">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>349</v>
+      </c>
+      <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
+        <v>319</v>
+      </c>
+      <c r="F157" t="b">
+        <v>1</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
+      </c>
+      <c r="N157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14">
+      <c r="A158" t="s">
+        <v>2</v>
+      </c>
+      <c r="B158" t="s">
+        <v>349</v>
+      </c>
+      <c r="D158" t="s">
+        <v>320</v>
+      </c>
+      <c r="E158" t="s">
+        <v>321</v>
+      </c>
+      <c r="F158" t="b">
+        <v>1</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
+      </c>
+      <c r="N158" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14">
+      <c r="A159" t="s">
+        <v>2</v>
+      </c>
+      <c r="B159" t="s">
+        <v>349</v>
+      </c>
+      <c r="D159" t="s">
+        <v>322</v>
+      </c>
+      <c r="E159" t="s">
+        <v>323</v>
+      </c>
+      <c r="F159" t="b">
+        <v>1</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
+      </c>
+      <c r="N159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>349</v>
+      </c>
+      <c r="D160" t="s">
+        <v>324</v>
+      </c>
+      <c r="E160" t="s">
+        <v>325</v>
+      </c>
+      <c r="F160" t="b">
+        <v>1</v>
+      </c>
+      <c r="H160" t="b">
+        <v>1</v>
+      </c>
+      <c r="N160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>349</v>
+      </c>
+      <c r="D161" t="s">
+        <v>326</v>
+      </c>
+      <c r="E161" t="s">
+        <v>327</v>
+      </c>
+      <c r="F161" t="b">
+        <v>1</v>
+      </c>
+      <c r="H161" t="b">
+        <v>1</v>
+      </c>
+      <c r="N161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162" t="s">
+        <v>2</v>
+      </c>
+      <c r="B162" t="s">
+        <v>349</v>
+      </c>
+      <c r="D162" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" t="s">
+        <v>328</v>
+      </c>
+      <c r="F162" t="b">
+        <v>1</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
+      </c>
+      <c r="P162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="A163" t="s">
+        <v>2</v>
+      </c>
+      <c r="B163" t="s">
+        <v>350</v>
+      </c>
+      <c r="D163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E163" t="s">
+        <v>301</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
+      <c r="H163" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>350</v>
+      </c>
+      <c r="D164" t="s">
+        <v>302</v>
+      </c>
+      <c r="E164" t="s">
+        <v>303</v>
+      </c>
+      <c r="F164" t="b">
+        <v>1</v>
+      </c>
+      <c r="H164" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>350</v>
+      </c>
+      <c r="D165" t="s">
+        <v>304</v>
+      </c>
+      <c r="E165" t="s">
+        <v>305</v>
+      </c>
+      <c r="F165" t="b">
+        <v>1</v>
+      </c>
+      <c r="H165" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17">
+      <c r="A166" t="s">
+        <v>2</v>
+      </c>
+      <c r="B166" t="s">
+        <v>350</v>
+      </c>
+      <c r="D166" t="s">
+        <v>80</v>
+      </c>
+      <c r="E166" t="s">
+        <v>256</v>
+      </c>
+      <c r="F166" t="b">
+        <v>1</v>
+      </c>
+      <c r="H166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17">
+      <c r="A167" t="s">
+        <v>2</v>
+      </c>
+      <c r="B167" t="s">
+        <v>350</v>
+      </c>
+      <c r="D167" t="s">
+        <v>225</v>
+      </c>
+      <c r="E167" t="s">
+        <v>257</v>
+      </c>
+      <c r="F167" t="b">
+        <v>1</v>
+      </c>
+      <c r="H167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17">
+      <c r="A168" t="s">
+        <v>2</v>
+      </c>
+      <c r="B168" t="s">
+        <v>350</v>
+      </c>
+      <c r="D168" t="s">
+        <v>250</v>
+      </c>
+      <c r="E168" t="s">
+        <v>258</v>
+      </c>
+      <c r="F168" t="b">
+        <v>1</v>
+      </c>
+      <c r="H168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17">
+      <c r="A169" t="s">
+        <v>2</v>
+      </c>
+      <c r="B169" t="s">
+        <v>350</v>
+      </c>
+      <c r="D169" t="s">
+        <v>252</v>
+      </c>
+      <c r="E169" t="s">
+        <v>259</v>
+      </c>
+      <c r="F169" t="b">
+        <v>1</v>
+      </c>
+      <c r="H169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17">
+      <c r="A170" t="s">
+        <v>2</v>
+      </c>
+      <c r="B170" t="s">
+        <v>350</v>
+      </c>
+      <c r="D170" t="s">
+        <v>131</v>
+      </c>
+      <c r="E170" t="s">
+        <v>260</v>
+      </c>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
+      <c r="H170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17">
+      <c r="A171" t="s">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>350</v>
+      </c>
+      <c r="D171" t="s">
+        <v>329</v>
+      </c>
+      <c r="E171" t="s">
+        <v>330</v>
+      </c>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
+      <c r="H171" t="b">
+        <v>1</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17">
+      <c r="A172" t="s">
+        <v>2</v>
+      </c>
+      <c r="B172" t="s">
+        <v>350</v>
+      </c>
+      <c r="D172" t="s">
+        <v>230</v>
+      </c>
+      <c r="E172" t="s">
+        <v>261</v>
+      </c>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
+      <c r="H172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17">
+      <c r="A173" t="s">
+        <v>2</v>
+      </c>
+      <c r="B173" t="s">
+        <v>350</v>
+      </c>
+      <c r="D173" t="s">
+        <v>241</v>
+      </c>
+      <c r="E173" t="s">
+        <v>306</v>
+      </c>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
+      <c r="H173" t="b">
+        <v>1</v>
+      </c>
+      <c r="M173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17">
+      <c r="A174" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>350</v>
+      </c>
+      <c r="D174" t="s">
+        <v>243</v>
+      </c>
+      <c r="E174" t="s">
+        <v>307</v>
+      </c>
+      <c r="F174" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" t="b">
+        <v>1</v>
+      </c>
+      <c r="N174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17">
+      <c r="A175" t="s">
+        <v>2</v>
+      </c>
+      <c r="B175" t="s">
+        <v>350</v>
+      </c>
+      <c r="D175" t="s">
+        <v>308</v>
+      </c>
+      <c r="E175" t="s">
+        <v>309</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" t="b">
+        <v>1</v>
+      </c>
+      <c r="N175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17">
+      <c r="A176" t="s">
+        <v>2</v>
+      </c>
+      <c r="B176" t="s">
+        <v>350</v>
+      </c>
+      <c r="D176" t="s">
+        <v>310</v>
+      </c>
+      <c r="E176" t="s">
+        <v>311</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" t="b">
+        <v>1</v>
+      </c>
+      <c r="N176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
+      <c r="A177" t="s">
+        <v>2</v>
+      </c>
+      <c r="B177" t="s">
+        <v>350</v>
+      </c>
+      <c r="D177" t="s">
+        <v>312</v>
+      </c>
+      <c r="E177" t="s">
+        <v>313</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+      <c r="H177" t="b">
+        <v>1</v>
+      </c>
+      <c r="N177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
+      <c r="A178" t="s">
+        <v>2</v>
+      </c>
+      <c r="B178" t="s">
+        <v>350</v>
+      </c>
+      <c r="D178" t="s">
+        <v>314</v>
+      </c>
+      <c r="E178" t="s">
+        <v>315</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+      <c r="H178" t="b">
+        <v>1</v>
+      </c>
+      <c r="N178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
+      <c r="A179" t="s">
+        <v>2</v>
+      </c>
+      <c r="B179" t="s">
+        <v>350</v>
+      </c>
+      <c r="D179" t="s">
+        <v>316</v>
+      </c>
+      <c r="E179" t="s">
+        <v>317</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+      <c r="H179" t="b">
+        <v>1</v>
+      </c>
+      <c r="N179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
+      <c r="A180" t="s">
+        <v>2</v>
+      </c>
+      <c r="B180" t="s">
+        <v>350</v>
+      </c>
+      <c r="D180" t="s">
+        <v>318</v>
+      </c>
+      <c r="E180" t="s">
+        <v>319</v>
+      </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
+      <c r="H180" t="b">
+        <v>1</v>
+      </c>
+      <c r="N180" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
+      <c r="A181" t="s">
+        <v>2</v>
+      </c>
+      <c r="B181" t="s">
+        <v>350</v>
+      </c>
+      <c r="D181" t="s">
+        <v>320</v>
+      </c>
+      <c r="E181" t="s">
+        <v>321</v>
+      </c>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
+      <c r="H181" t="b">
+        <v>1</v>
+      </c>
+      <c r="N181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
+      <c r="A182" t="s">
+        <v>2</v>
+      </c>
+      <c r="B182" t="s">
+        <v>350</v>
+      </c>
+      <c r="D182" t="s">
+        <v>322</v>
+      </c>
+      <c r="E182" t="s">
+        <v>323</v>
+      </c>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
+      </c>
+      <c r="N182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
+      <c r="A183" t="s">
+        <v>2</v>
+      </c>
+      <c r="B183" t="s">
+        <v>350</v>
+      </c>
+      <c r="D183" t="s">
+        <v>324</v>
+      </c>
+      <c r="E183" t="s">
+        <v>325</v>
+      </c>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
+      </c>
+      <c r="N183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16">
+      <c r="A184" t="s">
+        <v>2</v>
+      </c>
+      <c r="B184" t="s">
+        <v>350</v>
+      </c>
+      <c r="D184" t="s">
+        <v>326</v>
+      </c>
+      <c r="E184" t="s">
+        <v>327</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+      <c r="H184" t="b">
+        <v>1</v>
+      </c>
+      <c r="N184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
+      <c r="A185" t="s">
+        <v>2</v>
+      </c>
+      <c r="B185" t="s">
+        <v>350</v>
+      </c>
+      <c r="D185" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" t="s">
+        <v>328</v>
+      </c>
+      <c r="F185" t="b">
+        <v>1</v>
+      </c>
+      <c r="H185" t="b">
+        <v>1</v>
+      </c>
+      <c r="P185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16">
+      <c r="A186" t="s">
+        <v>2</v>
+      </c>
+      <c r="B186" t="s">
+        <v>351</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E186" t="s">
+        <v>256</v>
+      </c>
+      <c r="H186" t="b">
+        <v>1</v>
+      </c>
+      <c r="J186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16">
+      <c r="A187" t="s">
+        <v>2</v>
+      </c>
+      <c r="B187" t="s">
+        <v>351</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E187" t="s">
+        <v>257</v>
+      </c>
+      <c r="H187" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16">
+      <c r="A188" t="s">
+        <v>2</v>
+      </c>
+      <c r="B188" t="s">
+        <v>351</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E188" t="s">
+        <v>258</v>
+      </c>
+      <c r="H188" t="b">
+        <v>1</v>
+      </c>
+      <c r="J188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16">
+      <c r="A189" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" t="s">
+        <v>351</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E189" t="s">
+        <v>259</v>
+      </c>
+      <c r="H189" t="b">
+        <v>1</v>
+      </c>
+      <c r="J189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16">
+      <c r="A190" t="s">
+        <v>2</v>
+      </c>
+      <c r="B190" t="s">
+        <v>351</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E190" t="s">
+        <v>260</v>
+      </c>
+      <c r="H190" t="b">
+        <v>1</v>
+      </c>
+      <c r="J190" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16">
+      <c r="A191" t="s">
+        <v>2</v>
+      </c>
+      <c r="B191" t="s">
+        <v>351</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E191" t="s">
+        <v>261</v>
+      </c>
+      <c r="H191" t="b">
+        <v>1</v>
+      </c>
+      <c r="J191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16">
+      <c r="A192" t="s">
+        <v>2</v>
+      </c>
+      <c r="B192" t="s">
+        <v>352</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E192" t="s">
+        <v>256</v>
+      </c>
+      <c r="H192" t="b">
+        <v>1</v>
+      </c>
+      <c r="J192" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19">
+      <c r="A193" t="s">
+        <v>2</v>
+      </c>
+      <c r="B193" t="s">
+        <v>352</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E193" t="s">
+        <v>257</v>
+      </c>
+      <c r="H193" t="b">
+        <v>1</v>
+      </c>
+      <c r="J193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19">
+      <c r="A194" t="s">
+        <v>2</v>
+      </c>
+      <c r="B194" t="s">
+        <v>352</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E194" t="s">
+        <v>258</v>
+      </c>
+      <c r="H194" t="b">
+        <v>1</v>
+      </c>
+      <c r="J194" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19">
+      <c r="A195" t="s">
+        <v>2</v>
+      </c>
+      <c r="B195" t="s">
+        <v>352</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E195" t="s">
+        <v>259</v>
+      </c>
+      <c r="H195" t="b">
+        <v>1</v>
+      </c>
+      <c r="J195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19">
+      <c r="A196" t="s">
+        <v>2</v>
+      </c>
+      <c r="B196" t="s">
+        <v>352</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E196" t="s">
+        <v>260</v>
+      </c>
+      <c r="H196" t="b">
+        <v>1</v>
+      </c>
+      <c r="J196" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19">
+      <c r="A197" t="s">
+        <v>2</v>
+      </c>
+      <c r="B197" t="s">
+        <v>352</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E197" t="s">
+        <v>261</v>
+      </c>
+      <c r="H197" t="b">
+        <v>1</v>
+      </c>
+      <c r="J197" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19">
+      <c r="A198" t="s">
+        <v>2</v>
+      </c>
+      <c r="B198" t="s">
+        <v>353</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E198" t="s">
+        <v>256</v>
+      </c>
+      <c r="H198" t="b">
+        <v>1</v>
+      </c>
+      <c r="J198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19">
+      <c r="A199" t="s">
+        <v>2</v>
+      </c>
+      <c r="B199" t="s">
+        <v>353</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E199" t="s">
+        <v>257</v>
+      </c>
+      <c r="H199" t="b">
+        <v>1</v>
+      </c>
+      <c r="J199" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19">
+      <c r="A200" t="s">
+        <v>2</v>
+      </c>
+      <c r="B200" t="s">
+        <v>353</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E200" t="s">
+        <v>258</v>
+      </c>
+      <c r="H200" t="b">
+        <v>1</v>
+      </c>
+      <c r="J200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19">
+      <c r="A201" t="s">
+        <v>2</v>
+      </c>
+      <c r="B201" t="s">
+        <v>353</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E201" t="s">
+        <v>259</v>
+      </c>
+      <c r="H201" t="b">
+        <v>1</v>
+      </c>
+      <c r="J201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19">
+      <c r="A202" t="s">
+        <v>2</v>
+      </c>
+      <c r="B202" t="s">
+        <v>353</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E202" t="s">
+        <v>260</v>
+      </c>
+      <c r="H202" t="b">
+        <v>1</v>
+      </c>
+      <c r="J202" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19">
+      <c r="A203" t="s">
+        <v>2</v>
+      </c>
+      <c r="B203" t="s">
+        <v>353</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E203" t="s">
+        <v>261</v>
+      </c>
+      <c r="H203" t="b">
+        <v>1</v>
+      </c>
+      <c r="J203" t="b">
+        <v>1</v>
+      </c>
+      <c r="S203" s="2"/>
+    </row>
+    <row r="204" spans="1:19">
+      <c r="A204" t="s">
         <v>332</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B204" t="s">
         <v>331</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C204" t="s">
         <v>173</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D204" t="s">
         <v>174</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E204" t="s">
         <v>344</v>
       </c>
-      <c r="H138" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
+      <c r="H204" t="b">
+        <v>1</v>
+      </c>
+      <c r="S204" s="2"/>
+    </row>
+    <row r="205" spans="1:19">
+      <c r="A205" t="s">
         <v>332</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B205" t="s">
         <v>331</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C205" t="s">
         <v>67</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D205" t="s">
         <v>68</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E205" t="s">
         <v>336</v>
       </c>
-      <c r="F139" t="b">
-        <v>1</v>
-      </c>
-      <c r="H139" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="F205" t="b">
+        <v>1</v>
+      </c>
+      <c r="H205" t="b">
+        <v>1</v>
+      </c>
+      <c r="S205" s="2"/>
+    </row>
+    <row r="206" spans="1:19">
+      <c r="A206" t="s">
         <v>332</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B206" t="s">
         <v>331</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C206" t="s">
         <v>159</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D206" t="s">
         <v>160</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E206" t="s">
         <v>161</v>
       </c>
-      <c r="F140" t="b">
-        <v>1</v>
-      </c>
-      <c r="H140" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="F206" t="b">
+        <v>1</v>
+      </c>
+      <c r="H206" t="b">
+        <v>1</v>
+      </c>
+      <c r="S206" s="2"/>
+    </row>
+    <row r="207" spans="1:19">
+      <c r="A207" t="s">
         <v>332</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B207" t="s">
         <v>331</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C207" t="s">
         <v>167</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D207" t="s">
         <v>168</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E207" t="s">
         <v>169</v>
       </c>
-      <c r="F141" t="b">
-        <v>1</v>
-      </c>
-      <c r="H141" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
+      <c r="F207" t="b">
+        <v>1</v>
+      </c>
+      <c r="H207" t="b">
+        <v>1</v>
+      </c>
+      <c r="S207" s="2"/>
+    </row>
+    <row r="208" spans="1:19">
+      <c r="A208" t="s">
         <v>332</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B208" t="s">
         <v>331</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C208" t="s">
         <v>170</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D208" t="s">
         <v>171</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E208" t="s">
         <v>172</v>
       </c>
-      <c r="F142" t="b">
-        <v>1</v>
-      </c>
-      <c r="H142" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
+      <c r="F208" t="b">
+        <v>1</v>
+      </c>
+      <c r="H208" t="b">
+        <v>1</v>
+      </c>
+      <c r="S208" s="2"/>
+    </row>
+    <row r="209" spans="1:19">
+      <c r="A209" t="s">
         <v>332</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B209" t="s">
         <v>331</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C209" t="s">
         <v>113</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D209" t="s">
         <v>114</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E209" t="s">
         <v>175</v>
       </c>
-      <c r="F143" t="b">
-        <v>1</v>
-      </c>
-      <c r="H143" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
+      <c r="F209" t="b">
+        <v>1</v>
+      </c>
+      <c r="H209" t="b">
+        <v>1</v>
+      </c>
+      <c r="S209" s="2"/>
+    </row>
+    <row r="210" spans="1:19">
+      <c r="A210" t="s">
         <v>332</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B210" t="s">
         <v>331</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C210" t="s">
         <v>151</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D210" t="s">
         <v>152</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E210" t="s">
         <v>335</v>
       </c>
-      <c r="J144" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
+      <c r="J210" t="b">
+        <v>1</v>
+      </c>
+      <c r="S210" s="2"/>
+    </row>
+    <row r="211" spans="1:19">
+      <c r="A211" t="s">
         <v>332</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B211" t="s">
         <v>331</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C211" t="s">
         <v>162</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D211" t="s">
         <v>163</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E211" t="s">
         <v>164</v>
       </c>
-      <c r="F145" t="b">
-        <v>1</v>
-      </c>
-      <c r="H145" t="b">
-        <v>1</v>
-      </c>
-      <c r="J145" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="F211" t="b">
+        <v>1</v>
+      </c>
+      <c r="H211" t="b">
+        <v>1</v>
+      </c>
+      <c r="J211" t="b">
+        <v>1</v>
+      </c>
+      <c r="S211" s="2"/>
+    </row>
+    <row r="212" spans="1:19">
+      <c r="A212" t="s">
         <v>332</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B212" t="s">
         <v>331</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C212" t="s">
         <v>165</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D212" t="s">
         <v>99</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E212" t="s">
         <v>166</v>
       </c>
-      <c r="F146" t="b">
-        <v>1</v>
-      </c>
-      <c r="H146" t="b">
-        <v>1</v>
-      </c>
-      <c r="J146" t="b">
-        <v>1</v>
-      </c>
-      <c r="O146" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
+      <c r="F212" t="b">
+        <v>1</v>
+      </c>
+      <c r="H212" t="b">
+        <v>1</v>
+      </c>
+      <c r="J212" t="b">
+        <v>1</v>
+      </c>
+      <c r="O212" t="b">
+        <v>1</v>
+      </c>
+      <c r="S212" s="2"/>
+    </row>
+    <row r="213" spans="1:19">
+      <c r="A213" t="s">
         <v>332</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B213" t="s">
         <v>331</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C213" t="s">
         <v>144</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D213" t="s">
         <v>145</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E213" t="s">
         <v>146</v>
       </c>
-      <c r="F147" t="b">
-        <v>1</v>
-      </c>
-      <c r="H147" t="b">
-        <v>1</v>
-      </c>
-      <c r="I147" t="b">
-        <v>1</v>
-      </c>
-      <c r="J147" t="b">
-        <v>1</v>
-      </c>
-      <c r="O147" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
+      <c r="F213" t="b">
+        <v>1</v>
+      </c>
+      <c r="H213" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" t="b">
+        <v>1</v>
+      </c>
+      <c r="J213" t="b">
+        <v>1</v>
+      </c>
+      <c r="O213" t="b">
+        <v>1</v>
+      </c>
+      <c r="S213" s="2"/>
+    </row>
+    <row r="214" spans="1:19">
+      <c r="A214" t="s">
         <v>332</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B214" t="s">
         <v>331</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C214" t="s">
         <v>147</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D214" t="s">
         <v>148</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E214" t="s">
         <v>333</v>
       </c>
-      <c r="F148" t="b">
-        <v>1</v>
-      </c>
-      <c r="H148" t="b">
-        <v>1</v>
-      </c>
-      <c r="I148" t="b">
-        <v>1</v>
-      </c>
-      <c r="J148" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+      <c r="F214" t="b">
+        <v>1</v>
+      </c>
+      <c r="H214" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" t="b">
+        <v>1</v>
+      </c>
+      <c r="J214" t="b">
+        <v>1</v>
+      </c>
+      <c r="S214" s="2"/>
+    </row>
+    <row r="215" spans="1:19">
+      <c r="A215" t="s">
         <v>332</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B215" t="s">
         <v>331</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C215" t="s">
         <v>149</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D215" t="s">
         <v>150</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E215" t="s">
         <v>334</v>
       </c>
-      <c r="F149" t="b">
-        <v>1</v>
-      </c>
-      <c r="H149" t="b">
-        <v>1</v>
-      </c>
-      <c r="I149" t="b">
-        <v>1</v>
-      </c>
-      <c r="J149" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="F215" t="b">
+        <v>1</v>
+      </c>
+      <c r="H215" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" t="b">
+        <v>1</v>
+      </c>
+      <c r="J215" t="b">
+        <v>1</v>
+      </c>
+      <c r="S215" s="2"/>
+    </row>
+    <row r="216" spans="1:19">
+      <c r="A216" t="s">
         <v>332</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B216" t="s">
         <v>331</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C216" t="s">
         <v>153</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D216" t="s">
         <v>154</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E216" t="s">
         <v>155</v>
       </c>
-      <c r="F150" t="b">
-        <v>1</v>
-      </c>
-      <c r="H150" t="b">
-        <v>1</v>
-      </c>
-      <c r="I150" t="b">
-        <v>1</v>
-      </c>
-      <c r="J150" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="F216" t="b">
+        <v>1</v>
+      </c>
+      <c r="H216" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" t="b">
+        <v>1</v>
+      </c>
+      <c r="J216" t="b">
+        <v>1</v>
+      </c>
+      <c r="S216" s="2"/>
+    </row>
+    <row r="217" spans="1:19">
+      <c r="A217" t="s">
         <v>332</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B217" t="s">
         <v>331</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C217" t="s">
         <v>156</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D217" t="s">
         <v>157</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E217" t="s">
         <v>158</v>
       </c>
-      <c r="F151" t="b">
-        <v>1</v>
-      </c>
-      <c r="H151" t="b">
-        <v>1</v>
-      </c>
-      <c r="I151" t="b">
-        <v>1</v>
-      </c>
-      <c r="J151" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
+      <c r="F217" t="b">
+        <v>1</v>
+      </c>
+      <c r="H217" t="b">
+        <v>1</v>
+      </c>
+      <c r="I217" t="b">
+        <v>1</v>
+      </c>
+      <c r="J217" t="b">
+        <v>1</v>
+      </c>
+      <c r="S217" s="2"/>
+    </row>
+    <row r="218" spans="1:19">
+      <c r="A218" t="s">
         <v>332</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B218" t="s">
         <v>331</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C218" t="s">
         <v>176</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D218" t="s">
         <v>177</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E218" t="s">
         <v>178</v>
       </c>
-      <c r="F152" t="b">
-        <v>1</v>
-      </c>
-      <c r="H152" t="b">
-        <v>1</v>
-      </c>
-      <c r="I152" t="b">
-        <v>1</v>
-      </c>
-      <c r="J152" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
+      <c r="F218" t="b">
+        <v>1</v>
+      </c>
+      <c r="H218" t="b">
+        <v>1</v>
+      </c>
+      <c r="I218" t="b">
+        <v>1</v>
+      </c>
+      <c r="J218" t="b">
+        <v>1</v>
+      </c>
+      <c r="S218" s="2"/>
+    </row>
+    <row r="219" spans="1:19">
+      <c r="A219" t="s">
         <v>332</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B219" t="s">
         <v>331</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C219" t="s">
         <v>179</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D219" t="s">
         <v>180</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E219" t="s">
         <v>337</v>
       </c>
-      <c r="F153" t="b">
-        <v>1</v>
-      </c>
-      <c r="H153" t="b">
-        <v>1</v>
-      </c>
-      <c r="I153" t="b">
-        <v>1</v>
-      </c>
-      <c r="J153" t="b">
-        <v>1</v>
-      </c>
-      <c r="O153" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
+      <c r="F219" t="b">
+        <v>1</v>
+      </c>
+      <c r="H219" t="b">
+        <v>1</v>
+      </c>
+      <c r="I219" t="b">
+        <v>1</v>
+      </c>
+      <c r="J219" t="b">
+        <v>1</v>
+      </c>
+      <c r="O219" t="b">
+        <v>1</v>
+      </c>
+      <c r="S219" s="2"/>
+    </row>
+    <row r="220" spans="1:19">
+      <c r="A220" t="s">
         <v>345</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B220" t="s">
         <v>331</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C220" t="s">
         <v>346</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D220" t="s">
         <v>345</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E220" t="s">
         <v>347</v>
       </c>
-      <c r="F154" t="b">
-        <v>1</v>
-      </c>
-      <c r="H154" t="b">
-        <v>1</v>
-      </c>
-      <c r="K154" t="b">
+      <c r="F220" t="b">
+        <v>1</v>
+      </c>
+      <c r="H220" t="b">
+        <v>1</v>
+      </c>
+      <c r="K220" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4651,13 +6249,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB073B9-EDFA-B34E-9462-5C2B13CB19D1}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19.1640625" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>338</v>
       </c>
@@ -4668,7 +6266,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -4679,7 +6277,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -4690,7 +6288,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -4701,7 +6299,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4712,7 +6310,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4723,7 +6321,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -4734,7 +6332,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -4745,7 +6343,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4756,7 +6354,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -4767,7 +6365,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -4778,7 +6376,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -4789,7 +6387,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -4800,7 +6398,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -4811,7 +6409,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -4822,7 +6420,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -4833,7 +6431,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -4844,7 +6442,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -4855,7 +6453,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -4866,7 +6464,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -4877,7 +6475,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -4888,7 +6486,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -4899,7 +6497,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -4910,7 +6508,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -4921,7 +6519,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>88</v>
       </c>
@@ -4932,7 +6530,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -4943,7 +6541,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -4954,7 +6552,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>96</v>
       </c>
@@ -4965,7 +6563,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -4976,7 +6574,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -4987,7 +6585,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -4998,7 +6596,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -5009,7 +6607,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>111</v>
       </c>
@@ -5020,7 +6618,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>114</v>
       </c>
@@ -5031,7 +6629,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>117</v>
       </c>
@@ -5042,7 +6640,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>120</v>
       </c>
@@ -5053,7 +6651,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>123</v>
       </c>
@@ -5064,7 +6662,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -5075,7 +6673,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -5086,7 +6684,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -5097,7 +6695,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -5108,7 +6706,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -5119,7 +6717,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>139</v>
       </c>
@@ -5130,7 +6728,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>142</v>
       </c>
